--- a/i_test/test_D3_coorte_con_bears/med_digo.xlsx
+++ b/i_test/test_D3_coorte_con_bears/med_digo.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">ID</t>
   </si>
@@ -28,10 +28,7 @@
     <t xml:space="preserve">DATE</t>
   </si>
   <si>
-    <t xml:space="preserve">Table_cdm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ord</t>
+    <t xml:space="preserve">codvar</t>
   </si>
   <si>
     <t xml:space="preserve">aic</t>
@@ -85,15 +82,27 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE994"/>
+        <bgColor rgb="FFFFF5CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF5CE"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -101,6 +110,13 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -127,13 +143,29 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -145,6 +177,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFF5CE"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFE994"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -156,7 +248,7 @@
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -169,28 +261,29 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="B2" s="3" t="n">
+        <v>20250203</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>20250203</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>6</v>
-      </c>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="0" t="n">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="5" t="n">
         <v>20250203</v>
       </c>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
